--- a/sample_data/4_Minimal_Mandatory_Only.xlsx
+++ b/sample_data/4_Minimal_Mandatory_Only.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>401-100-200-000</t>
+          <t>999-400-100-000</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -466,7 +466,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>402-200-300-000</t>
+          <t>999-400-200-000</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>403-300-400-000</t>
+          <t>999-400-300-000</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -506,7 +506,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>404-400-500-000</t>
+          <t>999-400-400-000</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -526,7 +526,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>405-500-600-000</t>
+          <t>999-400-500-000</t>
         </is>
       </c>
       <c r="C6" t="n">
